--- a/アルゴリズムスケジュール/０２データベース.xlsx
+++ b/アルゴリズムスケジュール/０２データベース.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansh\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansh\OneDrive\Desktop\アルゴリズム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112B7172-A243-4E41-B204-892D491A76BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3FC5F6-1204-4BB3-8A72-5AC47BD6050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
+    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
   </bookViews>
   <sheets>
-    <sheet name="データベース基礎学習1日目" sheetId="1" r:id="rId1"/>
+    <sheet name="目次" sheetId="2" r:id="rId1"/>
+    <sheet name="データベース基礎学習1日目" sheetId="1" r:id="rId2"/>
+    <sheet name="データベース基本概念2日目" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="188">
   <si>
     <t>一問一答</t>
     <rPh sb="0" eb="4">
@@ -493,197 +495,568 @@
     <t>ACID特性の「A」は何か？</t>
   </si>
   <si>
+    <t>ACID特性の「C」は何か？</t>
+  </si>
+  <si>
+    <t>ACID特性の「I」は何か？</t>
+  </si>
+  <si>
+    <t>ACID特性の「D」は何か？</t>
+  </si>
+  <si>
+    <t>データベース設計の初期段階で行う作業は？</t>
+  </si>
+  <si>
+    <t>テーブル定義、主キー・外部キーの設定</t>
+  </si>
+  <si>
+    <t>NULL値とは何を意味するか？</t>
+  </si>
+  <si>
+    <t>未知・未入力の状態</t>
+  </si>
+  <si>
+    <t>データ独立性とは？</t>
+  </si>
+  <si>
+    <t>データ構造変更時にアプリへの影響が小さいこと</t>
+  </si>
+  <si>
+    <t>RDBで複数フィールドを主キーにする方法は？</t>
+  </si>
+  <si>
+    <t>複合主キー</t>
+  </si>
+  <si>
+    <t>varcharデータ型とは？</t>
+  </si>
+  <si>
+    <t>可変長文字列型</t>
+  </si>
+  <si>
+    <t>intデータ型とは？</t>
+  </si>
+  <si>
+    <t>整数型</t>
+  </si>
+  <si>
+    <t>dateデータ型とは？</t>
+  </si>
+  <si>
+    <t>日付型</t>
+  </si>
+  <si>
+    <t>参照整合性制約とは何か？</t>
+  </si>
+  <si>
+    <t>外部キーが参照する主キーが必ず存在すること</t>
+  </si>
+  <si>
+    <t>ドメイン制約とは何か？</t>
+  </si>
+  <si>
+    <t>データが指定された型や条件を満たす制約</t>
+  </si>
+  <si>
+    <t>一意性制約とは何か？</t>
+  </si>
+  <si>
+    <t>フィールド内の値が重複しない制約</t>
+  </si>
+  <si>
+    <t>候補キーとは？</t>
+  </si>
+  <si>
+    <t>主キーとして使用可能なフィールド</t>
+  </si>
+  <si>
+    <t>代替キーとは？</t>
+  </si>
+  <si>
+    <t>候補キーのうち主キーに選ばれなかったもの</t>
+  </si>
+  <si>
+    <t>スーパーキーとは？</t>
+  </si>
+  <si>
+    <t>一意にレコードを識別できるフィールドまたはフィールドの集合</t>
+  </si>
+  <si>
+    <t>NoSQLデータベースの代表例を挙げよ</t>
+  </si>
+  <si>
+    <t>MongoDB, Redisなど</t>
+  </si>
+  <si>
+    <t>関係型データベースで使う標準クエリ言語は？</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>SQLとは何の略か？</t>
+  </si>
+  <si>
+    <t>Structured Query Language</t>
+  </si>
+  <si>
+    <t>データベースの一元管理とは？</t>
+  </si>
+  <si>
+    <t>データを一箇所で管理し冗長性をなくすこと</t>
+  </si>
+  <si>
+    <t>データの整合性とは？</t>
+  </si>
+  <si>
+    <t>データが矛盾なく一貫した状態であること</t>
+  </si>
+  <si>
+    <t>関係型データベースの略称は？</t>
+  </si>
+  <si>
+    <t>RDB（Relational Database）</t>
+  </si>
+  <si>
+    <t>階層型データベースの代表例は？</t>
+  </si>
+  <si>
+    <t>IMS（Information Management System）</t>
+  </si>
+  <si>
+    <t>ネットワーク型データベースの代表例は？</t>
+  </si>
+  <si>
+    <t>Oracle Databaseの分類は？</t>
+  </si>
+  <si>
+    <t>関係型データベース</t>
+  </si>
+  <si>
+    <t>トランザクションでロールバックとは？</t>
+  </si>
+  <si>
+    <t>処理途中でエラーが発生した際、処理を元に戻すこと</t>
+  </si>
+  <si>
+    <t>トランザクションでコミットとは？</t>
+  </si>
+  <si>
+    <t>処理結果を確定し、データベースに反映すること</t>
+  </si>
+  <si>
+    <t>データベース正規化とは？</t>
+  </si>
+  <si>
+    <t>データの冗長性を排除し整合性を保つ設計手法</t>
+  </si>
+  <si>
+    <t>非正規化とは？</t>
+  </si>
+  <si>
+    <t>性能改善のため意図的に冗長性を許容すること</t>
+  </si>
+  <si>
+    <t>主キーに重複は許されるか？</t>
+  </si>
+  <si>
+    <t>外部キーに重複は許されるか？</t>
+  </si>
+  <si>
+    <t>許される</t>
+  </si>
+  <si>
+    <t>一貫性（Consistency）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>原子性（Atomicity）</t>
-  </si>
-  <si>
-    <t>ACID特性の「C」は何か？</t>
-  </si>
-  <si>
-    <t>一貫性（Consistency）</t>
-  </si>
-  <si>
-    <t>ACID特性の「I」は何か？</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>独立性（Isolation）</t>
-  </si>
-  <si>
-    <t>ACID特性の「D」は何か？</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>耐久性（Durability）</t>
-  </si>
-  <si>
-    <t>データベース設計の初期段階で行う作業は？</t>
-  </si>
-  <si>
-    <t>テーブル定義、主キー・外部キーの設定</t>
-  </si>
-  <si>
-    <t>NULL値とは何を意味するか？</t>
-  </si>
-  <si>
-    <t>未知・未入力の状態</t>
-  </si>
-  <si>
-    <t>データ独立性とは？</t>
-  </si>
-  <si>
-    <t>データ構造変更時にアプリへの影響が小さいこと</t>
-  </si>
-  <si>
-    <t>RDBで複数フィールドを主キーにする方法は？</t>
-  </si>
-  <si>
-    <t>複合主キー</t>
-  </si>
-  <si>
-    <t>varcharデータ型とは？</t>
-  </si>
-  <si>
-    <t>可変長文字列型</t>
-  </si>
-  <si>
-    <t>intデータ型とは？</t>
-  </si>
-  <si>
-    <t>整数型</t>
-  </si>
-  <si>
-    <t>dateデータ型とは？</t>
-  </si>
-  <si>
-    <t>日付型</t>
-  </si>
-  <si>
-    <t>参照整合性制約とは何か？</t>
-  </si>
-  <si>
-    <t>外部キーが参照する主キーが必ず存在すること</t>
-  </si>
-  <si>
-    <t>ドメイン制約とは何か？</t>
-  </si>
-  <si>
-    <t>データが指定された型や条件を満たす制約</t>
-  </si>
-  <si>
-    <t>一意性制約とは何か？</t>
-  </si>
-  <si>
-    <t>フィールド内の値が重複しない制約</t>
-  </si>
-  <si>
-    <t>候補キーとは？</t>
-  </si>
-  <si>
-    <t>主キーとして使用可能なフィールド</t>
-  </si>
-  <si>
-    <t>代替キーとは？</t>
-  </si>
-  <si>
-    <t>候補キーのうち主キーに選ばれなかったもの</t>
-  </si>
-  <si>
-    <t>スーパーキーとは？</t>
-  </si>
-  <si>
-    <t>一意にレコードを識別できるフィールドまたはフィールドの集合</t>
-  </si>
-  <si>
-    <t>NoSQLデータベースの代表例を挙げよ</t>
-  </si>
-  <si>
-    <t>MongoDB, Redisなど</t>
-  </si>
-  <si>
-    <t>関係型データベースで使う標準クエリ言語は？</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>SQLとは何の略か？</t>
-  </si>
-  <si>
-    <t>Structured Query Language</t>
-  </si>
-  <si>
-    <t>データベースの一元管理とは？</t>
-  </si>
-  <si>
-    <t>データを一箇所で管理し冗長性をなくすこと</t>
-  </si>
-  <si>
-    <t>データの整合性とは？</t>
-  </si>
-  <si>
-    <t>データが矛盾なく一貫した状態であること</t>
-  </si>
-  <si>
-    <t>関係型データベースの略称は？</t>
-  </si>
-  <si>
-    <t>RDB（Relational Database）</t>
-  </si>
-  <si>
-    <t>階層型データベースの代表例は？</t>
-  </si>
-  <si>
-    <t>IMS（Information Management System）</t>
-  </si>
-  <si>
-    <t>ネットワーク型データベースの代表例は？</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>CODASYL DBMS</t>
-  </si>
-  <si>
-    <t>Oracle Databaseの分類は？</t>
-  </si>
-  <si>
-    <t>関係型データベース</t>
-  </si>
-  <si>
-    <t>トランザクションでロールバックとは？</t>
-  </si>
-  <si>
-    <t>処理途中でエラーが発生した際、処理を元に戻すこと</t>
-  </si>
-  <si>
-    <t>トランザクションでコミットとは？</t>
-  </si>
-  <si>
-    <t>処理結果を確定し、データベースに反映すること</t>
-  </si>
-  <si>
-    <t>データベース正規化とは？</t>
-  </si>
-  <si>
-    <t>データの冗長性を排除し整合性を保つ設計手法</t>
-  </si>
-  <si>
-    <t>非正規化とは？</t>
-  </si>
-  <si>
-    <t>性能改善のため意図的に冗長性を許容すること</t>
-  </si>
-  <si>
-    <t>主キーに重複は許されるか？</t>
-  </si>
-  <si>
-    <t>外部キーに重複は許されるか？</t>
-  </si>
-  <si>
-    <t>許される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1日目</t>
+    <rPh sb="1" eb="3">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース基礎学習1日目</t>
+  </si>
+  <si>
+    <t>データベース基本概念2日目</t>
+  </si>
+  <si>
+    <t>2日目</t>
+    <rPh sb="1" eb="3">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベースで管理したい対象やオブジェクトを表す</t>
+    <rPh sb="7" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実体（エンティティ）とは、データとして管理すべき「もの」や「概念」のことで、ER図では諜報兼の箱で表現されます</t>
+    <rPh sb="0" eb="2">
+      <t>ジッタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ガイネン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>チョウホウケン</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データの冗長性（重複）を排除し、整合性を高めること</t>
+    <rPh sb="4" eb="7">
+      <t>ジョウチョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイジョ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>セイゴウセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解答</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解説</t>
+    <rPh sb="0" eb="2">
+      <t>カイセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規化を行うとデータの重複を防げるため、データ更新時に矛盾が生じるのを防止できます</t>
+    <rPh sb="0" eb="3">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>フセ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>コウシンジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ムジュン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ボウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第１正規形を満たし、主キーに部分的に依存している属性を別のテーブルに分離すること</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイキケイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ブブンテキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イゾン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ブンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第２正規形は、複合主キーに部分的に依存するデータを別テーブルに分割し、データを適切に管理します</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイキケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>フクゴウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ブブンテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イゾン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索時の処理性能（速度）を向上させるため。</t>
+    <rPh sb="0" eb="3">
+      <t>ケンサクジ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ショリセイノウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非正規化を行うとデータの冗長性が増える代わりに、データ検索や取得の速度が向上します。</t>
+    <rPh sb="0" eb="4">
+      <t>ヒセイキカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジョウチョウセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※JOINが少なくため</t>
+    <rPh sb="6" eb="7">
+      <t>スク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久性（Durability）</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久性とは、トランザクション処理が成功した後に、その結果が障害などが起きても永続的に保存される特性です。</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>エイゾク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>トクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ER図の問題</t>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>🔸 問題１【書籍管理】</t>
+  </si>
+  <si>
+    <t>以下の非正規形データをER図で表し、第1正規形へ正規化してください。</t>
+  </si>
+  <si>
+    <t>書籍（書籍番号, 書籍名, 著者名, 出版社名, 出版社住所, 著者連絡先）</t>
+  </si>
+  <si>
+    <t>🔸 問題２【学生の履修科目】</t>
+  </si>
+  <si>
+    <t>以下の第1正規形のデータを第2正規形へ正規化してください。</t>
+  </si>
+  <si>
+    <t>履修（学生番号, 科目コード, 学生名, 科目名, 単位数）</t>
+  </si>
+  <si>
+    <t>※学生番号と科目コードが複合主キー。</t>
+  </si>
+  <si>
+    <t>🔸 問題３【社員のプロジェクト管理】</t>
+  </si>
+  <si>
+    <t>以下の第1正規形データを第2正規形、さらに第3正規形に正規化してください。</t>
+  </si>
+  <si>
+    <t>社員プロジェクト（社員番号, プロジェクト番号, 社員名, プロジェクト名, 部署名, 部署所在地）</t>
+  </si>
+  <si>
+    <t>※社員番号とプロジェクト番号が複合主キー。</t>
+  </si>
+  <si>
+    <t>🔸 問題４【注文と商品管理】</t>
+  </si>
+  <si>
+    <t>以下のデータを第3正規形まで正規化し、適切なER図をdraw.ioで作成してください。</t>
+  </si>
+  <si>
+    <t>注文票（注文番号, 注文日, 顧客番号, 顧客名, 商品番号, 商品名, 商品価格, 注文数）</t>
+  </si>
+  <si>
+    <t>※注文番号と商品番号が複合主キー。</t>
+  </si>
+  <si>
+    <t>🔸 問題５【映画レンタル管理】</t>
+  </si>
+  <si>
+    <t>以下の非正規形データを第3正規形まで正規化し、適切なER図をdraw.ioで作成してください。</t>
+  </si>
+  <si>
+    <t>レンタル管理（レンタル番号, 顧客番号, 顧客名, 顧客住所, 映画番号, 映画タイトル, 映画ジャンル, レンタル日, 返却日）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,6 +1069,24 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -717,18 +1108,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -742,6 +1146,407 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>266732</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>31763</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7088806-05C7-FC34-1C1F-1208FA5B81DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="223838"/>
+          <a:ext cx="4381532" cy="1819288"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>147319</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>204871</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18B8EB97-25DA-5F31-81F0-19391AA0C3D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="2236304"/>
+          <a:ext cx="3581426" cy="1990740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>550419</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99342</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6256C874-6CCD-B803-E643-6DBCCFA87B0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="4472609"/>
+          <a:ext cx="5362614" cy="2781320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>261620</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>109829</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36E39813-D2AE-0DA7-2D12-3D6FEF490E44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="7379804"/>
+          <a:ext cx="3695727" cy="2124091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>159826</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>214060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3EA31B6-E0F6-D0C4-2678-C319FA9F33C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="9616109"/>
+          <a:ext cx="5657891" cy="3343299"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>469520</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>191754</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB025E93-0B8E-0985-81E8-53D9F6657201}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="687457" y="13194196"/>
+          <a:ext cx="4591084" cy="1533536"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>575641</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>45553</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>19116</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>183749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38CB07C0-06D9-AD81-F46E-CC69B017A456}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1263098" y="25199836"/>
+          <a:ext cx="9067866" cy="1924064"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>397565</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>169793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>55931</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>77047</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D56E9DF4-DE88-70A0-1034-17C4FBC9FC15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085022" y="20350370"/>
+          <a:ext cx="3095648" cy="2590819"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>443491</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>71783</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A90E0F2-6BD6-0AE6-7BB2-684CD133DF25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369392" y="28674392"/>
+          <a:ext cx="5921056" cy="3384826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1060,6 +1865,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C127F537-DC4F-42E1-9357-31E6446C0578}">
+  <dimension ref="B2:C3"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="3" max="3" width="24.4375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C2" location="データベース基礎学習1日目!A1" display="データベース基礎学習1日目" xr:uid="{013C98F6-3393-47FB-B3E6-B0D6FA932E38}"/>
+    <hyperlink ref="C3" location="データベース基本概念2日目!A1" display="データベース基本概念2日目" xr:uid="{08432263-DD5E-48F5-A347-9D25EA2F32F8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE45B1D-05B7-4B23-A958-6AC6B34471C2}">
   <dimension ref="B1:E50"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
@@ -1270,7 +2109,7 @@
         <v>84</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.7">
@@ -1278,10 +2117,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.7">
@@ -1289,10 +2128,10 @@
         <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.7">
@@ -1300,10 +2139,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.7">
@@ -1311,10 +2150,10 @@
         <v>22</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.7">
@@ -1322,10 +2161,10 @@
         <v>23</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.7">
@@ -1333,10 +2172,10 @@
         <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.7">
@@ -1344,10 +2183,10 @@
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.7">
@@ -1355,10 +2194,10 @@
         <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.7">
@@ -1366,10 +2205,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.7">
@@ -1377,10 +2216,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.7">
@@ -1388,10 +2227,10 @@
         <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.7">
@@ -1399,10 +2238,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.7">
@@ -1410,10 +2249,10 @@
         <v>31</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.7">
@@ -1421,10 +2260,10 @@
         <v>32</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.7">
@@ -1432,10 +2271,10 @@
         <v>33</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.7">
@@ -1443,10 +2282,10 @@
         <v>34</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.7">
@@ -1454,10 +2293,10 @@
         <v>35</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.7">
@@ -1465,10 +2304,10 @@
         <v>36</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.7">
@@ -1476,10 +2315,10 @@
         <v>37</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.7">
@@ -1487,10 +2326,10 @@
         <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.7">
@@ -1498,10 +2337,10 @@
         <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.7">
@@ -1509,10 +2348,10 @@
         <v>40</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.7">
@@ -1520,10 +2359,10 @@
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.7">
@@ -1531,10 +2370,10 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.7">
@@ -1542,10 +2381,10 @@
         <v>43</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.7">
@@ -1553,10 +2392,10 @@
         <v>44</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.7">
@@ -1564,10 +2403,10 @@
         <v>45</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.7">
@@ -1575,10 +2414,10 @@
         <v>46</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.7">
@@ -1586,10 +2425,10 @@
         <v>47</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.7">
@@ -1597,7 +2436,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>73</v>
@@ -1608,14 +2447,246 @@
         <v>49</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E266F503-5F95-4E4C-A8C4-80BF95FCBEDF}">
+  <dimension ref="A68:C160"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetData>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="B68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A69" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A73" t="s">
+        <v>157</v>
+      </c>
+      <c r="B73" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="B74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A75" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A76" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A78" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A79" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="B80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="B81" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A82" t="s">
+        <v>156</v>
+      </c>
+      <c r="B82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A83" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="B85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C86" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="C88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="C90" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C104" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C106" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C107" s="4"/>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C108" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C110" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C123" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C125" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C126" s="4"/>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C127" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C129" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C146" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C148" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C149" s="4"/>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C150" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C152" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C156" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C158" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C159" s="4"/>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C160" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/アルゴリズムスケジュール/０２データベース.xlsx
+++ b/アルゴリズムスケジュール/０２データベース.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansh\OneDrive\Desktop\アルゴリズム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3FC5F6-1204-4BB3-8A72-5AC47BD6050A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A690EA-6352-42F3-8937-A328E8D7ED96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
+    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
     <sheet name="データベース基礎学習1日目" sheetId="1" r:id="rId2"/>
     <sheet name="データベース基本概念2日目" sheetId="3" r:id="rId3"/>
+    <sheet name="ERモデル基礎3日目" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="190">
   <si>
     <t>一問一答</t>
     <rPh sb="0" eb="4">
@@ -1050,6 +1051,20 @@
   </si>
   <si>
     <t>レンタル管理（レンタル番号, 顧客番号, 顧客名, 顧客住所, 映画番号, 映画タイトル, 映画ジャンル, レンタル日, 返却日）</t>
+  </si>
+  <si>
+    <t>3日目</t>
+    <rPh sb="1" eb="3">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ERモデル基礎3日目</t>
+    <rPh sb="8" eb="10">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1161,7 +1176,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>266732</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>31763</xdr:rowOff>
+      <xdr:rowOff>33349</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1203,9 +1218,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>147319</xdr:colOff>
+      <xdr:colOff>144142</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>204871</xdr:rowOff>
+      <xdr:rowOff>201694</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1249,7 +1264,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>550419</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>99342</xdr:rowOff>
+      <xdr:rowOff>107278</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1291,9 +1306,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>261620</xdr:colOff>
+      <xdr:colOff>258443</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>109829</xdr:rowOff>
+      <xdr:rowOff>106652</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1335,9 +1350,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>159826</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>214060</xdr:rowOff>
+      <xdr:colOff>166175</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>4301</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1379,7 +1394,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>469520</xdr:colOff>
+      <xdr:colOff>471106</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>191754</xdr:rowOff>
     </xdr:to>
@@ -1425,7 +1440,7 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>19116</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>183749</xdr:rowOff>
+      <xdr:rowOff>185335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1511,9 +1526,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>443491</xdr:colOff>
+      <xdr:colOff>451427</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>71783</xdr:rowOff>
+      <xdr:rowOff>68606</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1538,6 +1553,935 @@
         <a:xfrm>
           <a:off x="1369392" y="28674392"/>
           <a:ext cx="5921056" cy="3384826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>467817</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>152289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F764FCC-8B25-8F16-6C0D-745639C91CC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369391" y="33815130"/>
+          <a:ext cx="7991533" cy="3686202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>341143</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>132119</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A585B340-DF82-0FDF-0478-3C8E7931ECD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369391" y="37790783"/>
+          <a:ext cx="5134013" cy="1457336"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>412256</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>48747</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{163E5138-A9B6-6F2A-5276-6C92390109C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369391" y="40943696"/>
+          <a:ext cx="7943908" cy="2257442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314786</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>35075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457E83B1-F5D7-A5B0-2A3B-6A0B60BAD9E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1369391" y="43373261"/>
+          <a:ext cx="6477047" cy="1581162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>485824</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>177808</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AFB2075-2937-4C8A-3105-5BE2EE705692}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="222250"/>
+          <a:ext cx="6658024" cy="1066808"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>171501</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>177822</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274C5116-909C-E3AA-AC85-2BAEA1330481}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1555750"/>
+          <a:ext cx="7029501" cy="3067072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200067</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>219096</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09ED8C28-1A97-E606-0A24-6758CC6059CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4889500"/>
+          <a:ext cx="5686467" cy="2886096"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304852</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>41303</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1324A093-EC9D-1B32-C07D-0CBEC3EDA18F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="8001000"/>
+          <a:ext cx="7162852" cy="3819553"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>181026</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>187372</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F31C0AA-7BDB-F4E5-0E28-059A84C731D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="12223750"/>
+          <a:ext cx="7039026" cy="6410372"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>276272</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>196877</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{702FDF28-E4B5-8B77-0E17-8AE4B365421C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="18891250"/>
+          <a:ext cx="6448472" cy="3752877"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>590599</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>63522</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E8634E5-313B-9426-8477-874C778E62D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="23114000"/>
+          <a:ext cx="6762799" cy="2952772"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266747</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>92097</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F97F52DA-F555-3D80-FCFC-CABA0D45A49E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="26447750"/>
+          <a:ext cx="6438947" cy="2981347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>504864</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>196873</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{654636AF-CBFE-1C06-D18E-82CFFFE79B85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="29781500"/>
+          <a:ext cx="5305464" cy="3086123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381038</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>142896</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83F093A7-3297-EC6E-9ED4-26F656AF1CC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="33115250"/>
+          <a:ext cx="5181638" cy="2809896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361983</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>3188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{468EAB56-AD70-1E18-7CE3-AB68FD09D2D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="36226750"/>
+          <a:ext cx="4476783" cy="1781188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>609650</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>6391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B2DE9E0-B776-26D4-E952-DFF5FEEECE94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="38449250"/>
+          <a:ext cx="6781850" cy="5562641"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>181026</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>12728</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6FF23F-595B-A64B-97A5-F73CFB0E4640}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="44227750"/>
+          <a:ext cx="7039026" cy="3790978"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>647750</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>215928</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB0A2650-8EC5-C6C1-D5A2-75D9955304C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="48228250"/>
+          <a:ext cx="6819950" cy="3771928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>235</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>238177</xdr:colOff>
+      <xdr:row>253</xdr:row>
+      <xdr:rowOff>104805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE36A120-36A6-8B71-92DC-2B69D95C09CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="52228750"/>
+          <a:ext cx="7096177" cy="4105305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542974</xdr:colOff>
+      <xdr:row>279</xdr:row>
+      <xdr:rowOff>152440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07F3856C-989E-3FC0-86EC-D71B1C72467D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="56673750"/>
+          <a:ext cx="6715174" cy="5486440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>444554</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>17481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21C6947C-B0FD-5C92-8390-A99C46676636}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6032500" y="33191450"/>
+          <a:ext cx="7442254" cy="2608281"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1866,7 +2810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C127F537-DC4F-42E1-9357-31E6446C0578}">
-  <dimension ref="B2:C3"/>
+  <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="3" max="3" width="24.4375" bestFit="1" customWidth="1"/>
@@ -1888,11 +2832,20 @@
         <v>149</v>
       </c>
     </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C2" location="データベース基礎学習1日目!A1" display="データベース基礎学習1日目" xr:uid="{013C98F6-3393-47FB-B3E6-B0D6FA932E38}"/>
     <hyperlink ref="C3" location="データベース基本概念2日目!A1" display="データベース基本概念2日目" xr:uid="{08432263-DD5E-48F5-A347-9D25EA2F32F8}"/>
+    <hyperlink ref="C4" location="ERモデル基礎3日目!A1" display="ERモデル基礎3日目" xr:uid="{A4F02723-139F-4DC2-8548-A877D80C1D4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2461,7 +3414,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E266F503-5F95-4E4C-A8C4-80BF95FCBEDF}">
-  <dimension ref="A68:C160"/>
+  <dimension ref="A68:C183"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="68" spans="1:2" x14ac:dyDescent="0.7">
@@ -2666,21 +3619,21 @@
         <v>184</v>
       </c>
     </row>
-    <row r="156" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
-      <c r="C156" s="3" t="s">
+    <row r="179" spans="3:3" ht="21.75" x14ac:dyDescent="0.7">
+      <c r="C179" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.7">
-      <c r="C158" t="s">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C181" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.7">
-      <c r="C159" s="4"/>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.7">
-      <c r="C160" s="4" t="s">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C182" s="4"/>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C183" s="4" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2689,4 +3642,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A8E23D-6085-4D49-BA39-8418C91848A8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/アルゴリズムスケジュール/０２データベース.xlsx
+++ b/アルゴリズムスケジュール/０２データベース.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mansh\OneDrive\Desktop\アルゴリズム\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A690EA-6352-42F3-8937-A328E8D7ED96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAA2AFE-8306-4A94-A761-1DBD4B5CA520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
+    <workbookView xWindow="-19310" yWindow="1300" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{EF282CF3-75C0-49EA-B41A-2C5BFB2D8B38}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
     <sheet name="データベース基礎学習1日目" sheetId="1" r:id="rId2"/>
     <sheet name="データベース基本概念2日目" sheetId="3" r:id="rId3"/>
     <sheet name="ERモデル基礎3日目" sheetId="4" r:id="rId4"/>
+    <sheet name="正規化理論4日目" sheetId="5" r:id="rId5"/>
+    <sheet name="論理設計のまとめ" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="285">
   <si>
     <t>一問一答</t>
     <rPh sb="0" eb="4">
@@ -1065,13 +1067,317 @@
       <t>ニチメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4日目</t>
+    <rPh sb="1" eb="3">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規化理論</t>
+    <rPh sb="0" eb="3">
+      <t>セイキカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リロン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5日目</t>
+    <rPh sb="1" eb="3">
+      <t>ニチメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>論理設計のまとめ</t>
+    <rPh sb="0" eb="4">
+      <t>ロンリセッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題</t>
+  </si>
+  <si>
+    <t>解答</t>
+  </si>
+  <si>
+    <t>論理設計とは何か？</t>
+  </si>
+  <si>
+    <t>概念設計をリレーショナルモデルに落とし込み、テーブル設計を行う工程。</t>
+  </si>
+  <si>
+    <t>リレーショナルデータベースでデータを格納する基本単位は？</t>
+  </si>
+  <si>
+    <t>テーブル（リレーション）。</t>
+  </si>
+  <si>
+    <t>リレーショナルデータベースで、行を指す用語は？</t>
+  </si>
+  <si>
+    <t>レコード（タプル）。</t>
+  </si>
+  <si>
+    <t>リレーショナルデータベースで、列を指す用語は？</t>
+  </si>
+  <si>
+    <t>カラム（属性）。</t>
+  </si>
+  <si>
+    <t>テーブル内の各レコードを一意に識別する。</t>
+  </si>
+  <si>
+    <t>外部キー（Foreign Key）とは何か？</t>
+  </si>
+  <si>
+    <t>他のテーブルの主キーを参照し、リレーションを定義するキー。</t>
+  </si>
+  <si>
+    <t>1対多（1:N）の関係をリレーショナルモデルで表現する方法は？</t>
+  </si>
+  <si>
+    <t>多側のテーブルに1側のテーブルの主キーを外部キーとして持たせる。</t>
+  </si>
+  <si>
+    <t>多対多（M:N）の関係をリレーショナルモデルで表現する方法は？</t>
+  </si>
+  <si>
+    <t>中間テーブルを作成し、各エンティティの主キーを外部キーとして格納する。</t>
+  </si>
+  <si>
+    <t>データの一貫性を保つために、データベース設計で考慮すべきものは？</t>
+  </si>
+  <si>
+    <t>参照整合性制約（Foreign Key制約）。</t>
+  </si>
+  <si>
+    <t>データベース設計で、データの冗長性を排除するために行うことは？</t>
+  </si>
+  <si>
+    <t>正規化。</t>
+  </si>
+  <si>
+    <t>第1正規形（1NF）の条件は？</t>
+  </si>
+  <si>
+    <t>各カラムの値が原子値（分割不可能な単位）であること。</t>
+  </si>
+  <si>
+    <t>第2正規形（2NF）の条件は？</t>
+  </si>
+  <si>
+    <t>1NFかつ、主キーの一部のみに依存する部分関数従属を排除すること。</t>
+  </si>
+  <si>
+    <t>第3正規形（3NF）の条件は？</t>
+  </si>
+  <si>
+    <t>2NFかつ、主キーに依存しない非キー属性間の依存関係（推移的関数従属）を排除すること。</t>
+  </si>
+  <si>
+    <t>第1正規形（1NF）で排除される問題は？</t>
+  </si>
+  <si>
+    <t>繰り返し属性（カラム内の複数値）。</t>
+  </si>
+  <si>
+    <t>第2正規形（2NF）で排除される問題は？</t>
+  </si>
+  <si>
+    <t>部分関数従属によるデータの不整合。</t>
+  </si>
+  <si>
+    <t>第3正規形（3NF）で排除される問題は？</t>
+  </si>
+  <si>
+    <t>推移的関数従属によるデータの冗長性。</t>
+  </si>
+  <si>
+    <t>第4正規形（4NF）の特徴は？</t>
+  </si>
+  <si>
+    <t>3NFかつ、多値従属性を排除。</t>
+  </si>
+  <si>
+    <t>第5正規形（5NF）の特徴は？</t>
+  </si>
+  <si>
+    <t>4NFかつ、結合従属性を排除。</t>
+  </si>
+  <si>
+    <t>正規化を行うメリットは？</t>
+  </si>
+  <si>
+    <t>データの整合性を保ち、冗長性を排除する。</t>
+  </si>
+  <si>
+    <t>正規化を行いすぎた場合のデメリットは？</t>
+  </si>
+  <si>
+    <t>テーブルの分割が多くなり、結合が増えてクエリのパフォーマンスが低下する。</t>
+  </si>
+  <si>
+    <t>データ型の選定で考慮すべき点は？</t>
+  </si>
+  <si>
+    <t>データの種類、サイズ、検索の効率。</t>
+  </si>
+  <si>
+    <t>日付型データを保存するのに適した型は？</t>
+  </si>
+  <si>
+    <t>DATE や DATETIME。</t>
+  </si>
+  <si>
+    <t>テキストデータの長さが可変の場合に適したデータ型は？</t>
+  </si>
+  <si>
+    <t>VARCHAR。</t>
+  </si>
+  <si>
+    <t>固定長の文字列データを格納する場合に適したデータ型は？</t>
+  </si>
+  <si>
+    <t>CHAR。</t>
+  </si>
+  <si>
+    <t>数値型で小数点以下の精度が必要な場合に適したデータ型は？</t>
+  </si>
+  <si>
+    <t>DECIMAL または FLOAT。</t>
+  </si>
+  <si>
+    <t>データ量が増えた場合のパフォーマンスを向上させるための対策は？</t>
+  </si>
+  <si>
+    <t>インデックスの適用。</t>
+  </si>
+  <si>
+    <t>一意性を確保するための制約は？</t>
+  </si>
+  <si>
+    <t>UNIQUE 制約。</t>
+  </si>
+  <si>
+    <t>NULL値を許可しないカラムの制約は？</t>
+  </si>
+  <si>
+    <t>NOT NULL 制約。</t>
+  </si>
+  <si>
+    <t>外部キー制約を設定する目的は？</t>
+  </si>
+  <si>
+    <t>参照整合性を保つため。</t>
+  </si>
+  <si>
+    <t>DELETE CASCADE の動作は？</t>
+  </si>
+  <si>
+    <t>親テーブルのデータ削除時に、関連する子テーブルのデータも削除される。</t>
+  </si>
+  <si>
+    <t>インデックスの役割は？</t>
+  </si>
+  <si>
+    <t>クエリの検索速度を向上させる。</t>
+  </si>
+  <si>
+    <t>主キーに自動的に作成されるインデックスの種類は？</t>
+  </si>
+  <si>
+    <t>クラスタ化インデックス（Clustered Index）。</t>
+  </si>
+  <si>
+    <t>検索頻度の高いカラムにインデックスを付与するときの注意点は？</t>
+  </si>
+  <si>
+    <t>インデックスの作成・更新コストが増加する。</t>
+  </si>
+  <si>
+    <t>インデックスを使用すると有効な操作は？</t>
+  </si>
+  <si>
+    <t>WHERE句による検索、ORDER BY、JOINの高速化。</t>
+  </si>
+  <si>
+    <t>インデックスを使用しても効果が少ない操作は？</t>
+  </si>
+  <si>
+    <t>INSERTやUPDATEの頻繁な実行。</t>
+  </si>
+  <si>
+    <t>インデックスの種類にはどのようなものがあるか？</t>
+  </si>
+  <si>
+    <t>B-treeインデックス、ハッシュインデックス、全文検索インデックスなど。</t>
+  </si>
+  <si>
+    <t>複数カラムに対するインデックスを何と呼ぶか？</t>
+  </si>
+  <si>
+    <t>複合インデックス（Composite Index）。</t>
+  </si>
+  <si>
+    <t>クエリの最適化に役立つインデックスの確認方法は？</t>
+  </si>
+  <si>
+    <t>EXPLAIN コマンド。</t>
+  </si>
+  <si>
+    <t>データの一貫性を保つために必要なルールは？</t>
+  </si>
+  <si>
+    <t>参照整合性制約。</t>
+  </si>
+  <si>
+    <t>エンティティの関係を明確にするために使う設計手法は？</t>
+  </si>
+  <si>
+    <t>ER図。</t>
+  </si>
+  <si>
+    <t>リレーショナルデータベースの3大設計工程は？</t>
+  </si>
+  <si>
+    <t>概念設計、論理設計、物理設計。</t>
+  </si>
+  <si>
+    <t>論理設計の目的は？</t>
+  </si>
+  <si>
+    <t>効率的なデータ構造を作る。</t>
+  </si>
+  <si>
+    <t>正規化と逆正規化の違いは？</t>
+  </si>
+  <si>
+    <t>正規化はデータの整合性を高め、逆正規化はパフォーマンスを向上させる。</t>
+  </si>
+  <si>
+    <t>SQLでテーブルを作成するコマンドは？</t>
+  </si>
+  <si>
+    <t>CREATE TABLE。</t>
+  </si>
+  <si>
+    <t>SQLでインデックスを作成するコマンドは？</t>
+  </si>
+  <si>
+    <t>CREATE INDEX。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1105,6 +1411,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1114,12 +1428,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1131,7 +1460,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1144,6 +1473,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2493,6 +2825,1160 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>361988</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>166693</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B1DE49E-0583-5AFD-E73C-2F91533E52EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5162588" cy="838206"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552474</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>204798</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9978ECBC-15E2-4B76-F695-454E9E69240E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1119188"/>
+          <a:ext cx="3295674" cy="1323985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219097</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>200036</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27EB920B-23FA-DCCA-6EA5-D0C4A3A2959A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2909888"/>
+          <a:ext cx="2962297" cy="1543061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>109939</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>202234</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D173294-B880-8804-8B15-AFB02301E684}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4692895"/>
+          <a:ext cx="4905411" cy="1543061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>205190</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>183184</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{884FFC7F-F28B-DBB3-A44C-D7B7C0E045C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6480664"/>
+          <a:ext cx="5000662" cy="1524011"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>300440</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>194917</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F78103-3E6D-C75F-26CA-4866D0E85F02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8268433"/>
+          <a:ext cx="5095912" cy="2876571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>100414</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>104797</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9828298-1316-DE75-E371-CCA621E422AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="11397029"/>
+          <a:ext cx="4895886" cy="3009922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>479942</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>63753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CBB799D-D17B-B062-6A26-1B7D19F55DCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14749096"/>
+          <a:ext cx="3905279" cy="1181109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>90889</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>119453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C80E7E7-4EDD-E05F-070F-1C98B078607B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="16089923"/>
+          <a:ext cx="4886361" cy="3248049"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>260128</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>33706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6157035E-F939-C654-BEC0-25BB0E1CF299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="19441991"/>
+          <a:ext cx="3000397" cy="257177"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>308490</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>139954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EC01F4D-2D90-7B38-8499-17084C0D1286}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="19888933"/>
+          <a:ext cx="3733827" cy="1257309"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>337804</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>86483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EF575D3-657F-A925-B63E-16958481E77E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="21229760"/>
+          <a:ext cx="4448208" cy="3438550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>167089</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>7337</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{173FC950-C5EF-2C9B-D6C8-E59C70E2DD23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="25028769"/>
+          <a:ext cx="4962561" cy="1571636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>223470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>62314</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>52776</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BE4F8A-2A64-F640-E0A8-5E57D43A0795}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="26816538"/>
+          <a:ext cx="4857786" cy="3181373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>10991</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>3663</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>329744</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>80620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCEE4C1D-518F-BFB8-616D-FAFF43768725}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5491529" y="26820201"/>
+          <a:ext cx="4429157" cy="3429025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>223471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>394954</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>79144</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06F253E1-79E6-198B-F0DA-98D448591D32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30615548"/>
+          <a:ext cx="4505358" cy="1866914"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>241133</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>46684</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB6F85BA-3E5E-51F0-9560-CDD3BA242016}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="32831690"/>
+          <a:ext cx="7105702" cy="6076994"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>469735</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>10875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1312FAC8-5FA4-EB2D-72BD-3DB82EEDE077}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="39085345"/>
+          <a:ext cx="7334304" cy="4924461"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>193508</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>72294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{214004C6-0394-7A48-94EB-40BD4CE970A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="44222276"/>
+          <a:ext cx="7058077" cy="4762535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>647735</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>109543</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F505274-6A64-7C6A-81E0-19FA9F5DEDF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="4762535" cy="781056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>472343</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>221054</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69C7D85D-9A9B-8F91-793A-9122781212B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1116724"/>
+          <a:ext cx="4591084" cy="1114433"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>578421</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>83435</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F6A5F52-8688-D485-8A79-79F961DEC6A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2456793"/>
+          <a:ext cx="3324249" cy="1200159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>177065</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>30553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60A63ED6-FFBF-29B8-C735-93342821CA8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3796862"/>
+          <a:ext cx="4295806" cy="923932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>453292</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83E4C50B-E161-210C-F932-7F19C79FC54F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5136931"/>
+          <a:ext cx="4572033" cy="2466993"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>81815</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>182954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD45F308-5A7E-2EDA-5462-DD508553DEE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7817069"/>
+          <a:ext cx="4200556" cy="1076333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>405667</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>78178</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3179C233-B536-4B1A-A2FC-1AB7F9213911}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9157138"/>
+          <a:ext cx="4524408" cy="971557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2810,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C127F537-DC4F-42E1-9357-31E6446C0578}">
-  <dimension ref="B2:C4"/>
+  <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="3" max="3" width="24.4375" bestFit="1" customWidth="1"/>
@@ -2840,12 +4326,30 @@
         <v>189</v>
       </c>
     </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.7">
+      <c r="B6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C2" location="データベース基礎学習1日目!A1" display="データベース基礎学習1日目" xr:uid="{013C98F6-3393-47FB-B3E6-B0D6FA932E38}"/>
     <hyperlink ref="C3" location="データベース基本概念2日目!A1" display="データベース基本概念2日目" xr:uid="{08432263-DD5E-48F5-A347-9D25EA2F32F8}"/>
     <hyperlink ref="C4" location="ERモデル基礎3日目!A1" display="ERモデル基礎3日目" xr:uid="{A4F02723-139F-4DC2-8548-A877D80C1D4A}"/>
+    <hyperlink ref="C5" location="正規化理論4日目!A1" display="正規化理論" xr:uid="{09A0896E-6CDD-4D60-9320-F5A28F69D953}"/>
+    <hyperlink ref="C6" location="論理設計のまとめ!A1" display="論理設計のまとめ" xr:uid="{AF7BBE72-A137-4B41-A22D-09A97BBE8963}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3653,4 +5157,399 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D13F65-7672-43FF-A1F1-4055945B6CC2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA33578-47EB-42E5-8CA6-3E5A60F20C30}">
+  <dimension ref="I1:J46"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="9" max="9" width="58" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="74.6875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I1" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I8" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I11" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I13" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I14" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I15" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I16" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I17" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I18" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I19" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I20" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I22" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I24" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I25" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I27" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I28" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I29" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I30" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I31" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I32" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I34" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I35" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="36" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="37" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I37" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I38" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I40" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="41" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I41" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I42" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I43" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I44" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="45" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I45" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="9:10" x14ac:dyDescent="0.7">
+      <c r="I46" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>